--- a/VT_Model_DMD_V01.xlsx
+++ b/VT_Model_DMD_V01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Model_MSc_SELECT\Model_MSc_SELECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C412ADA9-494A-482B-9257-65C644F6E272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6E06BB-874A-414A-B89C-A9BB35309855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEC_Comm" sheetId="112" r:id="rId1"/>
@@ -809,7 +809,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1029,6 +1029,9 @@
   <si>
     <t xml:space="preserve"> ENTSO data points</t>
   </si>
+  <si>
+    <t>FX</t>
+  </si>
 </sst>
 </file>
 
@@ -1058,7 +1061,7 @@
     <numFmt numFmtId="182" formatCode="yyyy"/>
     <numFmt numFmtId="183" formatCode="_-* ###0.00_-;\(###0.00\);_-* &quot;–&quot;_-;_-@_-"/>
     <numFmt numFmtId="184" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="186" formatCode="0.0"/>
+    <numFmt numFmtId="185" formatCode="0.0"/>
   </numFmts>
   <fonts count="112">
     <font>
@@ -3885,27 +3888,27 @@
     <xf numFmtId="0" fontId="5" fillId="39" borderId="19" xfId="791" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="43" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="43" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="43" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="43" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="185" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="184" fontId="5" fillId="39" borderId="19" xfId="791" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1263">
@@ -6823,7 +6826,9 @@
       <c r="E9" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="27"/>
+      <c r="F9" s="27" t="s">
+        <v>73</v>
+      </c>
       <c r="G9" s="27" t="s">
         <v>18</v>
       </c>
@@ -7197,46 +7202,46 @@
       <c r="B7" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="2:13" ht="15.75" customHeight="1">
       <c r="B8" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="41">
-        <f>C13*3.6</f>
+      <c r="C8" s="40">
+        <f t="shared" ref="C8:I8" si="0">C13*3.6</f>
         <v>393.80400000000003</v>
       </c>
-      <c r="D8" s="41">
-        <f>D13*3.6</f>
+      <c r="D8" s="40">
+        <f t="shared" si="0"/>
         <v>442.11863013698968</v>
       </c>
-      <c r="E8" s="41">
-        <f>E13*3.6</f>
+      <c r="E8" s="40">
+        <f t="shared" si="0"/>
         <v>565.20000000000005</v>
       </c>
-      <c r="F8" s="41">
-        <f>F13*3.6</f>
+      <c r="F8" s="40">
+        <f t="shared" si="0"/>
         <v>698.03424657534129</v>
       </c>
-      <c r="G8" s="41">
-        <f>G13*3.6</f>
+      <c r="G8" s="40">
+        <f t="shared" si="0"/>
         <v>828</v>
       </c>
-      <c r="H8" s="41">
-        <f>H13*3.6</f>
+      <c r="H8" s="40">
+        <f t="shared" si="0"/>
         <v>953.94986301369943</v>
       </c>
-      <c r="I8" s="41">
-        <f>I13*3.6</f>
+      <c r="I8" s="40">
+        <f t="shared" si="0"/>
         <v>1081.9076712328817</v>
       </c>
       <c r="L8" t="s">
@@ -7256,7 +7261,7 @@
       <c r="I9" s="25"/>
     </row>
     <row r="10" spans="2:13" ht="15.75" customHeight="1">
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="39" t="s">
         <v>70</v>
       </c>
       <c r="D10" s="25"/>
@@ -7303,34 +7308,34 @@
       <c r="B13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="37">
         <v>109.39</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="38">
         <f>_xlfn.FORECAST.LINEAR(2025,{109.39;157;230}, {2023;2030;2040})</f>
         <v>122.81073059360824</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="37">
         <v>157</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="38">
         <f>_xlfn.FORECAST.LINEAR(2035,{109.39;157;230}, {2023;2030;2040})</f>
         <v>193.89840182648368</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="37">
         <v>230</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="38">
         <f>_xlfn.FORECAST.LINEAR(2045,{109.39;157;230}, {2023;2030;2040})</f>
         <v>264.98607305936093</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="38">
         <f>_xlfn.FORECAST.LINEAR(2050,{109.39;157;230}, {2023;2030;2040})</f>
         <v>300.52990867580047</v>
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="36" t="s">
         <v>71</v>
       </c>
     </row>
@@ -7366,6 +7371,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E800C01780957C4993EAD0B0EDC5E8FF" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1ada55d1baadc38a59b37f146ad1da21">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95645557-b925-4e14-b9c3-bb0dccab904e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6148ddbe210b331c9edc42bf7e0f90a" ns2:_="">
     <xsd:import namespace="95645557-b925-4e14-b9c3-bb0dccab904e"/>
@@ -7509,35 +7529,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{476A49FA-039E-4D8A-A3EF-E37AC40E343E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="95645557-b925-4e14-b9c3-bb0dccab904e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7559,9 +7554,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{476A49FA-039E-4D8A-A3EF-E37AC40E343E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="95645557-b925-4e14-b9c3-bb0dccab904e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>